--- a/artfynd/A 52446-2025 artfynd.xlsx
+++ b/artfynd/A 52446-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83273131</v>
+        <v>83273034</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515067.4696933806</v>
+        <v>514976</v>
       </c>
       <c r="R2" t="n">
-        <v>6383991.823211099</v>
+        <v>6384045</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,7 +744,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>3E78A671-FC6B-45CE-8991-EC25702DF77F</t>
+          <t>26656CCE-AF48-4D65-AB14-D55D617786B6</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -757,19 +752,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83273130</v>
+        <v>83273036</v>
       </c>
       <c r="B3" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515081.4316399012</v>
+        <v>515122</v>
       </c>
       <c r="R3" t="n">
-        <v>6383991.33920972</v>
+        <v>6383985</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +854,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>8168957C-0A5A-4EED-B007-36B0985F4677</t>
+          <t>7234E5D2-7850-449C-9680-611100E67089</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -882,19 +862,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83273876</v>
+        <v>83273037</v>
       </c>
       <c r="B4" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515016.4105849405</v>
+        <v>515100</v>
       </c>
       <c r="R4" t="n">
-        <v>6384005.567015014</v>
+        <v>6384035</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -999,7 +964,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>D4108C2B-3D2F-46EF-A2EC-37BD12D87C32</t>
+          <t>AC3F9CF6-CD16-401F-B0D6-38724E76949F</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1007,19 +972,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83273062</v>
+        <v>83273038</v>
       </c>
       <c r="B5" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515029.2609101635</v>
+        <v>515089</v>
       </c>
       <c r="R5" t="n">
-        <v>6384015.260615769</v>
+        <v>6384040</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1124,7 +1074,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>F6ECE4A4-296F-45D1-B318-30E7CE097221</t>
+          <t>914BEAB3-3916-48BA-BC01-10C7C00ECF96</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1132,19 +1082,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,15 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83273870</v>
+        <v>83273039</v>
       </c>
       <c r="B6" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515002.432839253</v>
+        <v>515077</v>
       </c>
       <c r="R6" t="n">
-        <v>6384010.338295065</v>
+        <v>6384041</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1249,7 +1184,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>E1398BD9-0CA2-4E93-B8FE-9B82695DA346</t>
+          <t>6BC5C766-B051-4A9E-BA01-716FB33347E8</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1257,19 +1192,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>83273875</v>
+        <v>83273043</v>
       </c>
       <c r="B7" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514998.0780416363</v>
+        <v>514979</v>
       </c>
       <c r="R7" t="n">
-        <v>6384026.398832598</v>
+        <v>6384040</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1374,7 +1294,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>C74C0162-0AAF-42B3-BF4D-44B4FB542943</t>
+          <t>44C4A4B2-137A-4A4A-9FAD-78C8841C1B12</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1382,19 +1302,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,15 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>83273139</v>
+        <v>83273046</v>
       </c>
       <c r="B8" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515079.8706846384</v>
+        <v>515034</v>
       </c>
       <c r="R8" t="n">
-        <v>6383977.936090246</v>
+        <v>6384001</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1499,7 +1404,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>F9CB3B6E-E318-4B2E-A301-FE1899904C1E</t>
+          <t>B219EE37-F011-42B7-AD50-162BB0A2FF8D</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1507,19 +1412,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,15 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>83273046</v>
+        <v>83273047</v>
       </c>
       <c r="B9" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515033.607898159</v>
+        <v>515028</v>
       </c>
       <c r="R9" t="n">
-        <v>6384001.343599697</v>
+        <v>6383994</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1624,7 +1514,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>B219EE37-F011-42B7-AD50-162BB0A2FF8D</t>
+          <t>4B92BD14-B831-4873-A020-3229F42D0264</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1632,19 +1522,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,15 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>83273550</v>
+        <v>83273062</v>
       </c>
       <c r="B10" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515062.981278775</v>
+        <v>515029</v>
       </c>
       <c r="R10" t="n">
-        <v>6384043.787699572</v>
+        <v>6384015</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1749,7 +1624,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>812F860F-9CD1-43D5-937A-7C0573B954B3</t>
+          <t>F6ECE4A4-296F-45D1-B318-30E7CE097221</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1757,19 +1632,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,15 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>83273871</v>
+        <v>83273077</v>
       </c>
       <c r="B11" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515024.0286913335</v>
+        <v>515011</v>
       </c>
       <c r="R11" t="n">
-        <v>6383978.264754657</v>
+        <v>6384045</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1874,7 +1734,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A6D87ED1-390D-4D88-B313-7186C41DDB06</t>
+          <t>3B030B83-3AD1-4547-AEB9-37FF24EE4871</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1882,19 +1742,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,15 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>83273873</v>
+        <v>83273090</v>
       </c>
       <c r="B12" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515013.7795454203</v>
+        <v>514957</v>
       </c>
       <c r="R12" t="n">
-        <v>6383991.088224832</v>
+        <v>6384062</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1999,7 +1844,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>CB696598-5789-4754-9658-6BB961193F46</t>
+          <t>246FB825-17DD-4F14-A9F2-DE28BCFF219C</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2007,19 +1852,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,15 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>83273037</v>
+        <v>83273130</v>
       </c>
       <c r="B13" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,10 +1924,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515100.0602944946</v>
+        <v>515081</v>
       </c>
       <c r="R13" t="n">
-        <v>6384035.351406256</v>
+        <v>6383991</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2124,7 +1954,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>AC3F9CF6-CD16-401F-B0D6-38724E76949F</t>
+          <t>8168957C-0A5A-4EED-B007-36B0985F4677</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2132,19 +1962,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2175,15 +1995,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>83273039</v>
+        <v>83273131</v>
       </c>
       <c r="B14" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515076.9510137707</v>
+        <v>515067</v>
       </c>
       <c r="R14" t="n">
-        <v>6384041.160179293</v>
+        <v>6383992</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2249,7 +2064,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>6BC5C766-B051-4A9E-BA01-716FB33347E8</t>
+          <t>3E78A671-FC6B-45CE-8991-EC25702DF77F</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2257,19 +2072,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2300,15 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>83273868</v>
+        <v>83273139</v>
       </c>
       <c r="B15" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2344,10 +2144,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515013.7676436605</v>
+        <v>515080</v>
       </c>
       <c r="R15" t="n">
-        <v>6383994.303529715</v>
+        <v>6383978</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2374,7 +2174,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>572DEE84-2B75-470B-8742-1848C7E2A769</t>
+          <t>F9CB3B6E-E318-4B2E-A301-FE1899904C1E</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2382,19 +2182,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2425,15 +2215,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>83273047</v>
+        <v>83273550</v>
       </c>
       <c r="B16" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,10 +2254,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515027.7275888025</v>
+        <v>515063</v>
       </c>
       <c r="R16" t="n">
-        <v>6383994.355227823</v>
+        <v>6384044</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2499,7 +2284,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>4B92BD14-B831-4873-A020-3229F42D0264</t>
+          <t>812F860F-9CD1-43D5-937A-7C0573B954B3</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2507,19 +2292,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2550,15 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>83273077</v>
+        <v>83273851</v>
       </c>
       <c r="B17" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2594,10 +2364,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515010.8946287259</v>
+        <v>515007</v>
       </c>
       <c r="R17" t="n">
-        <v>6384045.202249004</v>
+        <v>6384006</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2624,7 +2394,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>3B030B83-3AD1-4547-AEB9-37FF24EE4871</t>
+          <t>991CABA6-B27E-485A-8BAC-C5FA2A19E67F</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2632,19 +2402,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2675,15 +2435,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>83273877</v>
+        <v>83273865</v>
       </c>
       <c r="B18" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2719,10 +2474,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515004.5765497977</v>
+        <v>515060</v>
       </c>
       <c r="R18" t="n">
-        <v>6384011.418003007</v>
+        <v>6383940</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2749,7 +2504,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>FE4B1287-DA46-4C11-8F58-D02C153C87ED</t>
+          <t>F892FBF7-513D-404A-BFAC-14735412F44E</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2757,19 +2512,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2800,15 +2545,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>83273851</v>
+        <v>83273868</v>
       </c>
       <c r="B19" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2844,10 +2584,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515007.2809710111</v>
+        <v>515014</v>
       </c>
       <c r="R19" t="n">
-        <v>6384006.069114817</v>
+        <v>6383994</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2874,7 +2614,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>991CABA6-B27E-485A-8BAC-C5FA2A19E67F</t>
+          <t>572DEE84-2B75-470B-8742-1848C7E2A769</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2882,19 +2622,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2925,15 +2655,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>83273038</v>
+        <v>83273869</v>
       </c>
       <c r="B20" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,10 +2694,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515088.767125955</v>
+        <v>515032</v>
       </c>
       <c r="R20" t="n">
-        <v>6384040.132349234</v>
+        <v>6383946</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2999,7 +2724,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>914BEAB3-3916-48BA-BC01-10C7C00ECF96</t>
+          <t>3CD2E6A5-FBA5-45E9-BB65-9BB8DA38D190</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3007,19 +2732,9 @@
           <t>2007-07-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2007-07-04</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3043,6 +2758,666 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>83273870</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norrsånna, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>515002</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6384010</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Edshult</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>E1398BD9-0CA2-4E93-B8FE-9B82695DA346</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2007-07-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2007-07-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson, Malin Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>83273871</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norrsånna, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>515024</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6383978</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Edshult</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A6D87ED1-390D-4D88-B313-7186C41DDB06</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2007-07-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2007-07-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson, Malin Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>83273873</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norrsånna, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>515014</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6383991</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Edshult</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>CB696598-5789-4754-9658-6BB961193F46</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2007-07-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2007-07-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson, Malin Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>83273875</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norrsånna, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>514998</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6384026</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Edshult</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>C74C0162-0AAF-42B3-BF4D-44B4FB542943</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2007-07-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2007-07-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson, Malin Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>83273876</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norrsånna, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>515016</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6384006</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Edshult</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D4108C2B-3D2F-46EF-A2EC-37BD12D87C32</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2007-07-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2007-07-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson, Malin Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>83273877</v>
+      </c>
+      <c r="B26" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norrsånna, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>515005</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6384011</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Edshult</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>FE4B1287-DA46-4C11-8F58-D02C153C87ED</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2007-07-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2007-07-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson, Malin Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>

--- a/artfynd/A 52446-2025 artfynd.xlsx
+++ b/artfynd/A 52446-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273034</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273036</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273037</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273038</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273039</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273043</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273046</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273047</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273062</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273077</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1882,6 +1937,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273090</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1992,6 +2052,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273130</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2102,6 +2167,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273131</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2212,6 +2282,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273139</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2322,6 +2397,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273550</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2432,6 +2512,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273851</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2542,6 +2627,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273865</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2652,6 +2742,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273868</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2762,6 +2857,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273869</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2872,6 +2972,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273870</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2982,6 +3087,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273871</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3092,6 +3202,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273873</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3202,6 +3317,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273875</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3312,6 +3432,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273876</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3422,8 +3547,40 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83273877</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>